--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2024_valparaiso.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2024_valparaiso.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 16:46</t>
+    <t xml:space="preserve">2026-09-09 19:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2024_valparaiso.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2024_valparaiso.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 19:11</t>
+    <t xml:space="preserve">2026-09-17 04:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2024_valparaiso.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2024_valparaiso.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 04:26</t>
+    <t xml:space="preserve">2026-09-25 11:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2024_valparaiso.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2024_valparaiso.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-25 11:20</t>
+    <t xml:space="preserve">2026-09-26 23:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2024_valparaiso.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2024_valparaiso.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t xml:space="preserve">Territorio</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">Reg_Mujeres</t>
   </si>
   <si>
-    <t xml:space="preserve">Valparaiso</t>
+    <t xml:space="preserve">Valparaíso</t>
   </si>
   <si>
     <t xml:space="preserve">Campo</t>
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-26 23:53</t>
+    <t xml:space="preserve">2026-10-05 05:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Unidad territorial</t>
   </si>
   <si>
-    <t xml:space="preserve">Region de Valparaiso</t>
+    <t xml:space="preserve">Region de Valparaíso</t>
   </si>
   <si>
     <t xml:space="preserve">Año</t>
@@ -96,9 +96,6 @@
   </si>
   <si>
     <t xml:space="preserve">Ratio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valparaíso</t>
   </si>
   <si>
     <t xml:space="preserve">Isla de Pascua</t>
@@ -738,7 +735,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>51</v>
@@ -749,7 +746,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>52</v>
@@ -760,7 +757,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>53</v>
@@ -771,7 +768,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>54</v>
@@ -782,7 +779,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>55</v>
@@ -793,7 +790,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>56</v>
@@ -804,7 +801,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>57</v>
@@ -815,7 +812,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>58</v>
